--- a/tech/android/PO/PO_about.xlsx
+++ b/tech/android/PO/PO_about.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10713"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/project/YingVickyCao.github.io/tech/android/PO/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A76658C-B079-FD44-BBA6-B15ACD836AD4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28660" windowHeight="14400" firstSheet="4" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Homepage" sheetId="14" r:id="rId1"/>
@@ -20,17 +26,27 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Good_app!$H$7:$J$10</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Microsoft Office User</author>
   </authors>
   <commentList>
-    <comment ref="G24" authorId="0">
+    <comment ref="G24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
       <text>
         <r>
           <rPr>
@@ -61,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="126">
   <si>
     <t>Page</t>
   </si>
@@ -448,14 +464,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="32">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -557,143 +567,27 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -720,13 +614,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -754,176 +648,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="33">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1235,256 +961,20 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="29" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1551,7 +1041,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1575,9 +1065,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1626,20 +1113,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1670,7 +1145,7 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="25"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1679,88 +1154,64 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="25" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="3" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="25" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="50" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="5">
+    <cellStyle name="Bad" xfId="3" builtinId="27"/>
+    <cellStyle name="Hyperlink" xfId="4" builtinId="8"/>
+    <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink 2" xfId="1"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="60% - Accent6" xfId="3" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="4" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="5" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="6" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="7" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="8" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="9" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="10" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="11" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="12" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="13" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="14" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="15" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="16" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="17" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="18" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="19" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="21" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="22" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="23" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="24" builtinId="32"/>
-    <cellStyle name="Bad" xfId="25" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="26" builtinId="42"/>
-    <cellStyle name="Total" xfId="27" builtinId="25"/>
-    <cellStyle name="Output" xfId="28" builtinId="21"/>
-    <cellStyle name="Currency" xfId="29" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="30" builtinId="38"/>
-    <cellStyle name="Note" xfId="31" builtinId="10"/>
-    <cellStyle name="Input" xfId="32" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="33" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="34" builtinId="22"/>
-    <cellStyle name="Good" xfId="35" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="36" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="37" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="38" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="39" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="40" builtinId="50"/>
-    <cellStyle name="Title" xfId="41" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="42" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="43" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="44" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="45" builtinId="17"/>
-    <cellStyle name="Comma" xfId="46" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="47" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="48" builtinId="40"/>
-    <cellStyle name="Percent" xfId="49" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="50" builtinId="8"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="0000FA00"/>
+      <color rgb="FF00FA00"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1772,7 +1223,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1798,6 +1248,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-CN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1820,8 +1271,6 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr/>
-          <c:explosion val="0"/>
           <c:dPt>
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
@@ -1836,6 +1285,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-01FD-CB4F-A4BC-7481E6DDB90F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1851,6 +1305,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-01FD-CB4F-A4BC-7481E6DDB90F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1866,6 +1325,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-01FD-CB4F-A4BC-7481E6DDB90F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1881,6 +1345,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-01FD-CB4F-A4BC-7481E6DDB90F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -1909,6 +1378,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-CN"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
@@ -1919,25 +1389,22 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
             </c:extLst>
           </c:dLbls>
           <c:cat>
@@ -1967,20 +1434,25 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.454545454545455</c:v>
+                  <c:v>0.45454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.424242424242424</c:v>
+                  <c:v>0.42424242424242425</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0909090909090909</c:v>
+                  <c:v>9.0909090909090912E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0303030303030303</c:v>
+                  <c:v>3.0303030303030304E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-01FD-CB4F-A4BC-7481E6DDB90F}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2003,7 +1475,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2029,6 +1500,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-CN"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -2058,6 +1530,7 @@
       <a:pPr>
         <a:defRPr lang="en-US"/>
       </a:pPr>
+      <a:endParaRPr lang="en-CN"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3402,7 +2875,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{4DD99D25-FEBC-9D48-AEA7-5CEFA1E1E825}" cxnId="{D7553E25-429C-0B40-BE06-83986E6FB46A}" type="parTrans">
+    <dgm:pt modelId="{4DD99D25-FEBC-9D48-AEA7-5CEFA1E1E825}" type="parTrans" cxnId="{D7553E25-429C-0B40-BE06-83986E6FB46A}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3413,7 +2886,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{6459DB3E-061F-A047-A27E-E7CEAAB57CD4}" cxnId="{D7553E25-429C-0B40-BE06-83986E6FB46A}" type="sibTrans">
+    <dgm:pt modelId="{6459DB3E-061F-A047-A27E-E7CEAAB57CD4}" type="sibTrans" cxnId="{D7553E25-429C-0B40-BE06-83986E6FB46A}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3438,7 +2911,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{02EEEC49-7ABE-1343-8B21-01A02B88C714}" cxnId="{021F1772-78B8-AD42-BBEC-1547531409CA}" type="parTrans">
+    <dgm:pt modelId="{02EEEC49-7ABE-1343-8B21-01A02B88C714}" type="parTrans" cxnId="{021F1772-78B8-AD42-BBEC-1547531409CA}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3449,7 +2922,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{D3B682CB-01A3-324E-8C98-1676C3B698B3}" cxnId="{021F1772-78B8-AD42-BBEC-1547531409CA}" type="sibTrans">
+    <dgm:pt modelId="{D3B682CB-01A3-324E-8C98-1676C3B698B3}" type="sibTrans" cxnId="{021F1772-78B8-AD42-BBEC-1547531409CA}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3474,7 +2947,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{B63FFA3D-5AA6-4846-97A0-24BE294C8154}" cxnId="{0B582214-0A45-2C41-97A5-89E10318CC16}" type="parTrans">
+    <dgm:pt modelId="{B63FFA3D-5AA6-4846-97A0-24BE294C8154}" type="parTrans" cxnId="{0B582214-0A45-2C41-97A5-89E10318CC16}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3485,7 +2958,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{EE25B7B0-4F0A-804D-A2C3-1444F8CBC770}" cxnId="{0B582214-0A45-2C41-97A5-89E10318CC16}" type="sibTrans">
+    <dgm:pt modelId="{EE25B7B0-4F0A-804D-A2C3-1444F8CBC770}" type="sibTrans" cxnId="{0B582214-0A45-2C41-97A5-89E10318CC16}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3518,7 +2991,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{F9CE9E5D-298D-8546-AC41-6BF085995F8E}" cxnId="{2C610ABD-C837-4040-9C45-0B6D4FE404B3}" type="parTrans">
+    <dgm:pt modelId="{F9CE9E5D-298D-8546-AC41-6BF085995F8E}" type="parTrans" cxnId="{2C610ABD-C837-4040-9C45-0B6D4FE404B3}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3529,7 +3002,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{C62E7DFD-5825-9342-B4A8-4E1D2A7E207E}" cxnId="{2C610ABD-C837-4040-9C45-0B6D4FE404B3}" type="sibTrans">
+    <dgm:pt modelId="{C62E7DFD-5825-9342-B4A8-4E1D2A7E207E}" type="sibTrans" cxnId="{2C610ABD-C837-4040-9C45-0B6D4FE404B3}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3554,7 +3027,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{CA01D36F-9BDF-0242-8FF6-9111B92915FA}" cxnId="{2944A67E-925B-9741-9B15-F9FA24FD7A41}" type="parTrans">
+    <dgm:pt modelId="{CA01D36F-9BDF-0242-8FF6-9111B92915FA}" type="parTrans" cxnId="{2944A67E-925B-9741-9B15-F9FA24FD7A41}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3565,7 +3038,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{77B58ED7-87D9-E74D-B83F-7ED7C2A10E46}" cxnId="{2944A67E-925B-9741-9B15-F9FA24FD7A41}" type="sibTrans">
+    <dgm:pt modelId="{77B58ED7-87D9-E74D-B83F-7ED7C2A10E46}" type="sibTrans" cxnId="{2944A67E-925B-9741-9B15-F9FA24FD7A41}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3590,7 +3063,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{43B01633-9E76-6B4F-8843-79593CB0D8D7}" cxnId="{1F73EDC8-59E0-D845-A330-E2B09D83BBC6}" type="parTrans">
+    <dgm:pt modelId="{43B01633-9E76-6B4F-8843-79593CB0D8D7}" type="parTrans" cxnId="{1F73EDC8-59E0-D845-A330-E2B09D83BBC6}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3601,7 +3074,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{292D1D67-BEB9-9946-8578-0A447688593C}" cxnId="{1F73EDC8-59E0-D845-A330-E2B09D83BBC6}" type="sibTrans">
+    <dgm:pt modelId="{292D1D67-BEB9-9946-8578-0A447688593C}" type="sibTrans" cxnId="{1F73EDC8-59E0-D845-A330-E2B09D83BBC6}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3626,7 +3099,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{D1777041-E888-3C4A-8EC5-2418A1513C54}" cxnId="{E21F2596-EAAB-D341-9CCF-C96A92643475}" type="parTrans">
+    <dgm:pt modelId="{D1777041-E888-3C4A-8EC5-2418A1513C54}" type="parTrans" cxnId="{E21F2596-EAAB-D341-9CCF-C96A92643475}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3637,7 +3110,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{51E5D6D4-EA96-6444-BCF9-775E8CB8BBD5}" cxnId="{E21F2596-EAAB-D341-9CCF-C96A92643475}" type="sibTrans">
+    <dgm:pt modelId="{51E5D6D4-EA96-6444-BCF9-775E8CB8BBD5}" type="sibTrans" cxnId="{E21F2596-EAAB-D341-9CCF-C96A92643475}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3662,7 +3135,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{06D726B7-DB2D-684D-9585-2B1CF5B1AC57}" cxnId="{00CA5E10-FA23-F249-84EC-31B8B6630A39}" type="parTrans">
+    <dgm:pt modelId="{06D726B7-DB2D-684D-9585-2B1CF5B1AC57}" type="parTrans" cxnId="{00CA5E10-FA23-F249-84EC-31B8B6630A39}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3673,7 +3146,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{64FC3F20-8C71-7047-ABB6-A498B6F8E45C}" cxnId="{00CA5E10-FA23-F249-84EC-31B8B6630A39}" type="sibTrans">
+    <dgm:pt modelId="{64FC3F20-8C71-7047-ABB6-A498B6F8E45C}" type="sibTrans" cxnId="{00CA5E10-FA23-F249-84EC-31B8B6630A39}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3698,7 +3171,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{FAA47813-0834-A94A-8611-78698F50CCA0}" cxnId="{5B46A980-EBE7-764F-8D5D-5D46927CCA5D}" type="parTrans">
+    <dgm:pt modelId="{FAA47813-0834-A94A-8611-78698F50CCA0}" type="parTrans" cxnId="{5B46A980-EBE7-764F-8D5D-5D46927CCA5D}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3709,7 +3182,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{FC383B57-8F52-0342-9A4F-5982F615F0C2}" cxnId="{5B46A980-EBE7-764F-8D5D-5D46927CCA5D}" type="sibTrans">
+    <dgm:pt modelId="{FC383B57-8F52-0342-9A4F-5982F615F0C2}" type="sibTrans" cxnId="{5B46A980-EBE7-764F-8D5D-5D46927CCA5D}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3734,7 +3207,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{84DA8EC6-9C9C-7045-83F1-F79783F704D5}" cxnId="{BE03DC3E-17EF-3947-BF1D-6C3F8580DB4B}" type="parTrans">
+    <dgm:pt modelId="{84DA8EC6-9C9C-7045-83F1-F79783F704D5}" type="parTrans" cxnId="{BE03DC3E-17EF-3947-BF1D-6C3F8580DB4B}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3745,7 +3218,7 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
-    <dgm:pt modelId="{C6DEB497-36E7-2E45-B29E-D05B826CB237}" cxnId="{BE03DC3E-17EF-3947-BF1D-6C3F8580DB4B}" type="sibTrans">
+    <dgm:pt modelId="{C6DEB497-36E7-2E45-B29E-D05B826CB237}" type="sibTrans" cxnId="{BE03DC3E-17EF-3947-BF1D-6C3F8580DB4B}">
       <dgm:prSet/>
       <dgm:spPr/>
       <dgm:t>
@@ -3966,6 +3439,11 @@
   </dgm:cxnLst>
   <dgm:bg/>
   <dgm:whole/>
+  <dgm:extLst>
+    <a:ext uri="http://schemas.microsoft.com/office/drawing/2008/diagram">
+      <dsp:dataModelExt xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" relId="rId5" minVer="http://schemas.openxmlformats.org/drawingml/2006/diagram"/>
+    </a:ext>
+  </dgm:extLst>
 </dgm:dataModel>
 </file>
 
@@ -5552,6 +5030,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5571,6 +5050,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5590,6 +5070,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5609,6 +5090,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5630,6 +5112,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5651,6 +5134,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5672,6 +5156,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5693,6 +5178,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5714,6 +5200,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5735,6 +5222,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5754,6 +5242,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5773,6 +5262,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5792,6 +5282,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="0">
@@ -5811,6 +5302,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="0">
@@ -5832,6 +5324,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5851,6 +5344,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5870,6 +5364,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="0">
@@ -5889,6 +5384,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5908,6 +5404,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5927,6 +5424,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5946,6 +5444,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5965,6 +5464,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -5984,6 +5484,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6003,6 +5504,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6022,6 +5524,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6041,6 +5544,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="0">
@@ -6062,6 +5566,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6083,6 +5588,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6104,6 +5610,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6125,6 +5632,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6146,6 +5654,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6167,6 +5676,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6188,6 +5698,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6207,6 +5718,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6226,6 +5738,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6245,6 +5758,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6264,6 +5778,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6285,6 +5800,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6306,6 +5822,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6327,6 +5844,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6348,6 +5866,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="0">
@@ -6367,6 +5886,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="1">
@@ -6386,6 +5906,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="0">
@@ -6407,6 +5928,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6426,6 +5948,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6445,6 +5968,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6464,6 +5988,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="1">
@@ -6483,6 +6008,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="0">
@@ -6502,6 +6028,7 @@
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </dgm:scene3d>
+    <dgm:sp3d/>
     <dgm:txPr/>
     <dgm:style>
       <a:lnRef idx="2">
@@ -6522,7 +6049,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -6536,9 +6063,15 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="6" name="Straight Arrow Connector 5"/>
+        <xdr:cNvPr id="6" name="Straight Arrow Connector 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -6585,13 +6118,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Graphic 7" descr="User"/>
+        <xdr:cNvPr id="8" name="Graphic 7" descr="User">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -6629,13 +6168,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Graphic 11" descr="Group"/>
+        <xdr:cNvPr id="12" name="Graphic 11" descr="Group">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -6671,9 +6216,15 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="13" name="Straight Arrow Connector 12"/>
+        <xdr:cNvPr id="13" name="Straight Arrow Connector 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -6720,13 +6271,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Graphic 14" descr="Hierarchy"/>
+        <xdr:cNvPr id="15" name="Graphic 14" descr="Hierarchy">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -6764,13 +6321,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Graphic 16" descr="Smart Phone"/>
+        <xdr:cNvPr id="17" name="Graphic 16" descr="Smart Phone">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -6806,9 +6369,15 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="Straight Arrow Connector 20"/>
+        <xdr:cNvPr id="21" name="Straight Arrow Connector 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -6853,9 +6422,15 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="22" name="Straight Arrow Connector 21"/>
+        <xdr:cNvPr id="22" name="Straight Arrow Connector 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -6891,7 +6466,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -6907,13 +6482,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Graphic 2" descr="Right Pointing Backhand Index "/>
+        <xdr:cNvPr id="3" name="Graphic 2" descr="Right Pointing Backhand Index ">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -6949,9 +6530,15 @@
       <xdr:row>36</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Right Arrow 6"/>
+        <xdr:cNvPr id="7" name="Right Arrow 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7004,9 +6591,15 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="Can 10" descr="跨进程通信机制"/>
+        <xdr:cNvPr id="11" name="Can 10" descr="跨进程通信机制">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7060,9 +6653,15 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="15" name="Straight Arrow Connector 14"/>
+        <xdr:cNvPr id="15" name="Straight Arrow Connector 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -7107,9 +6706,15 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="20" name="Straight Arrow Connector 19"/>
+        <xdr:cNvPr id="20" name="Straight Arrow Connector 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -7154,9 +6759,15 @@
       <xdr:row>34</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="Up Arrow 21"/>
+        <xdr:cNvPr id="22" name="Up Arrow 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7209,9 +6820,15 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="Down Arrow 22"/>
+        <xdr:cNvPr id="23" name="Down Arrow 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7264,9 +6881,15 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="Right Arrow 23"/>
+        <xdr:cNvPr id="24" name="Right Arrow 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7319,9 +6942,15 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="Right Arrow 24"/>
+        <xdr:cNvPr id="25" name="Right Arrow 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7374,9 +7003,15 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="Snip Same Side Corner Rectangle 32"/>
+        <xdr:cNvPr id="33" name="Snip Same Side Corner Rectangle 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7471,19 +7106,6 @@
             </a:rPr>
             <a:t>ViewTree</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="1" cap="none" spc="0">
-            <a:ln w="0"/>
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst>
-              <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
-                <a:schemeClr val="dk1">
-                  <a:alpha val="40000"/>
-                </a:schemeClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -7503,19 +7125,6 @@
             </a:rPr>
             <a:t>Measure</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" cap="none" spc="0">
-            <a:ln w="0"/>
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst>
-              <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
-                <a:schemeClr val="dk1">
-                  <a:alpha val="40000"/>
-                </a:schemeClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -7535,19 +7144,6 @@
             </a:rPr>
             <a:t>Layout</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" cap="none" spc="0">
-            <a:ln w="0"/>
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst>
-              <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
-                <a:schemeClr val="dk1">
-                  <a:alpha val="40000"/>
-                </a:schemeClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
@@ -7567,19 +7163,6 @@
             </a:rPr>
             <a:t>Draw</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" cap="none" spc="0">
-            <a:ln w="0"/>
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst>
-              <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
-                <a:schemeClr val="dk1">
-                  <a:alpha val="40000"/>
-                </a:schemeClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7598,9 +7181,15 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="Snip Same Side Corner Rectangle 34"/>
+        <xdr:cNvPr id="35" name="Snip Same Side Corner Rectangle 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7654,9 +7243,15 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="Cloud 35"/>
+        <xdr:cNvPr id="36" name="Cloud 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7744,9 +7339,15 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="Double Brace 38"/>
+        <xdr:cNvPr id="39" name="Double Brace 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7804,9 +7405,15 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="Right Arrow 42"/>
+        <xdr:cNvPr id="43" name="Right Arrow 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7859,9 +7466,15 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="Rounded Rectangle 41"/>
+        <xdr:cNvPr id="42" name="Rounded Rectangle 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7898,7 +7511,6 @@
             <a:rPr lang="en-US" sz="1100"/>
             <a:t>显卡</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7917,9 +7529,15 @@
       <xdr:row>35</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="Right Arrow 44"/>
+        <xdr:cNvPr id="45" name="Right Arrow 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7974,13 +7592,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="2015072408335049"/>
+        <xdr:cNvPr id="6" name="Picture 5" descr="2015072408335049">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8012,13 +7636,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="2015072408335048"/>
+        <xdr:cNvPr id="8" name="Picture 7" descr="2015072408335048">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8039,7 +7669,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -8053,9 +7683,15 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="8" name="Straight Arrow Connector 7"/>
+        <xdr:cNvPr id="8" name="Straight Arrow Connector 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -8100,9 +7736,15 @@
       <xdr:row>33</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="Straight Arrow Connector 10"/>
+        <xdr:cNvPr id="11" name="Straight Arrow Connector 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -8147,9 +7789,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>310445</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="Double Brace 17"/>
+        <xdr:cNvPr id="18" name="Double Brace 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8200,9 +7848,15 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>42334</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="Double Brace 18"/>
+        <xdr:cNvPr id="19" name="Double Brace 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8244,7 +7898,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -8258,9 +7912,15 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 1"/>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8297,7 +7957,6 @@
             <a:rPr lang="en-US" sz="4000"/>
             <a:t>Foreground</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="4000"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8316,9 +7975,15 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle 2"/>
+        <xdr:cNvPr id="3" name="Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8358,7 +8023,6 @@
             <a:rPr lang="en-US" sz="4000"/>
             <a:t>Background</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="4000"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8377,9 +8041,15 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Rectangle 3"/>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8419,7 +8089,6 @@
             <a:rPr lang="en-US" sz="1100"/>
             <a:t>Foreground Service</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8438,9 +8107,15 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Rectangle 4"/>
+        <xdr:cNvPr id="5" name="Rectangle 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8480,7 +8155,6 @@
             <a:rPr lang="en-US" sz="1100"/>
             <a:t>Background Service</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8499,9 +8173,15 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="Straight Arrow Connector 6"/>
+        <xdr:cNvPr id="7" name="Straight Arrow Connector 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="3"/>
           <a:endCxn id="4" idx="1"/>
@@ -8552,9 +8232,15 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="Straight Arrow Connector 8"/>
+        <xdr:cNvPr id="9" name="Straight Arrow Connector 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="3"/>
         </xdr:cNvCxnSpPr>
@@ -8604,9 +8290,15 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="Straight Arrow Connector 10"/>
+        <xdr:cNvPr id="11" name="Straight Arrow Connector 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -8654,9 +8346,15 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Rectangle 11"/>
+        <xdr:cNvPr id="12" name="Rectangle 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8696,7 +8394,6 @@
             <a:rPr lang="en-US" sz="4000"/>
             <a:t>Background in whitelist</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="4000"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8715,9 +8412,15 @@
       <xdr:row>22</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="Straight Arrow Connector 13"/>
+        <xdr:cNvPr id="14" name="Straight Arrow Connector 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="12" idx="3"/>
           <a:endCxn id="4" idx="1"/>
@@ -8765,9 +8468,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="Straight Arrow Connector 15"/>
+        <xdr:cNvPr id="16" name="Straight Arrow Connector 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -8812,9 +8521,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Up Arrow 5"/>
+        <xdr:cNvPr id="6" name="Up Arrow 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8857,7 +8572,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
@@ -8871,14 +8586,20 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart 7"/>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7376795" y="2336800"/>
-        <a:ext cx="3924300" cy="2743200"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8892,7 +8613,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -8906,14 +8627,20 @@
       <xdr:row>27</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Diagram 2"/>
+        <xdr:cNvPr id="3" name="Diagram 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4673600" y="2857500"/>
-        <a:ext cx="4419600" cy="2743200"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/diagram">
@@ -9178,260 +8905,256 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" outlineLevelCol="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.1642857142857" customWidth="1"/>
-    <col min="2" max="2" width="12.3285714285714" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="44" spans="1:1">
-      <c r="A1" s="115" t="s">
+    <row r="1" spans="1:2" ht="47" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="116" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="111" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="31"/>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="116" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="111" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="116" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="111" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="116" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="111" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="9"/>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="9"/>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="9"/>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="9"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="9"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="9"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="9"/>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="9"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="9"/>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" location="Good_app!A1" display="Good_app"/>
-    <hyperlink ref="A3" location="'Guide to background processing'!A1" display="Guide to background processing"/>
-    <hyperlink ref="A4" location="'Background Execution Limits'!A1" display="Background Execution Limits"/>
-    <hyperlink ref="A5" location="'C2_绘制优化_Overdraw_CustomView'!A1" display="C2_绘制优化_Overdraw_CustomView"/>
+    <hyperlink ref="A2" location="Good_app!A1" display="Good_app" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A3" location="'Guide to background processing'!A1" display="Guide to background processing" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A4" location="'Background Execution Limits'!A1" display="Background Execution Limits" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A5" location="'C2_绘制优化_Overdraw_CustomView'!A1" display="C2_绘制优化_Overdraw_CustomView" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="D3:J17"/>
-  <sheetFormatPr defaultColWidth="10.8285714285714" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="8" width="10.8285714285714" style="109"/>
-    <col min="9" max="9" width="10.8285714285714" style="110"/>
-    <col min="10" max="16384" width="10.8285714285714" style="109"/>
+    <col min="1" max="8" width="10.83203125" style="104"/>
+    <col min="9" max="9" width="10.83203125" style="105"/>
+    <col min="10" max="16384" width="10.83203125" style="104"/>
   </cols>
   <sheetData>
-    <row r="3" spans="6:6">
-      <c r="F3" s="111" t="s">
+    <row r="3" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="F3" s="106" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="10:10">
-      <c r="J4" s="111" t="s">
+    <row r="4" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="J4" s="106" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="4:9">
-      <c r="D7" s="111" t="s">
+    <row r="7" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D7" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="112" t="s">
+      <c r="E7" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="111" t="s">
+      <c r="H7" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="112" t="s">
+      <c r="I7" s="107" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" s="108" customFormat="1" spans="4:9">
-      <c r="D8" s="108" t="s">
+    <row r="8" spans="4:10" s="103" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D8" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="113" t="s">
+      <c r="E8" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="108" t="s">
+      <c r="H8" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="114" t="s">
+      <c r="I8" s="109" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="5:6">
-      <c r="E16" s="111"/>
-      <c r="F16" s="111" t="s">
+    <row r="16" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="E16" s="106"/>
+      <c r="F16" s="106" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="10:10">
-      <c r="J17" s="111" t="s">
+    <row r="17" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J17" s="106" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="10.6642857142857" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.6642857142857" style="102"/>
-    <col min="2" max="2" width="9.16428571428571" style="102" customWidth="1"/>
-    <col min="3" max="3" width="14" style="102" customWidth="1"/>
-    <col min="4" max="16384" width="10.6642857142857" style="102"/>
+    <col min="1" max="1" width="10.6640625" style="97"/>
+    <col min="2" max="2" width="9.1640625" style="97" customWidth="1"/>
+    <col min="3" max="3" width="14" style="97" customWidth="1"/>
+    <col min="4" max="16384" width="10.6640625" style="97"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="103" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="103" t="s">
+      <c r="B1" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="103" t="s">
+      <c r="C1" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="103">
+      <c r="D1" s="98">
         <v>100</v>
       </c>
-      <c r="E1" s="103">
+      <c r="E1" s="98">
         <v>500</v>
       </c>
-      <c r="F1" s="103">
+      <c r="F1" s="98">
         <v>1000</v>
       </c>
-      <c r="G1" s="103">
+      <c r="G1" s="98">
         <v>5000</v>
       </c>
-      <c r="H1" s="103">
+      <c r="H1" s="98">
         <v>65536</v>
       </c>
-      <c r="I1" s="103">
+      <c r="I1" s="98">
         <v>100000</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="104" t="s">
+      <c r="C2" s="99" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="27">
@@ -9453,14 +9176,14 @@
         <v>16016</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="27" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="104" t="s">
+      <c r="C3" s="99" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="27">
@@ -9482,101 +9205,101 @@
         <v>10627</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="105" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="100" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="100" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="105" t="s">
+      <c r="C4" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="105">
+      <c r="D4" s="100">
         <v>0</v>
       </c>
-      <c r="E4" s="105">
+      <c r="E4" s="100">
         <v>0</v>
       </c>
-      <c r="F4" s="105">
+      <c r="F4" s="100">
         <v>0</v>
       </c>
-      <c r="G4" s="105">
+      <c r="G4" s="100">
         <v>0</v>
       </c>
-      <c r="H4" s="105">
+      <c r="H4" s="100">
         <v>9714854</v>
       </c>
-      <c r="I4" s="105">
+      <c r="I4" s="100">
         <v>9774632</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="105" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="100" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="105" t="s">
+      <c r="C5" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="105">
+      <c r="D5" s="100">
         <v>0</v>
       </c>
-      <c r="E5" s="105">
+      <c r="E5" s="100">
         <v>0</v>
       </c>
-      <c r="F5" s="105">
+      <c r="F5" s="100">
         <v>0</v>
       </c>
-      <c r="G5" s="105">
+      <c r="G5" s="100">
         <v>0</v>
       </c>
-      <c r="H5" s="105">
+      <c r="H5" s="100">
         <v>4340983</v>
       </c>
-      <c r="I5" s="105">
+      <c r="I5" s="100">
         <v>6257528</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="27" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="104" t="s">
+      <c r="C6" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="106">
+      <c r="D6" s="101">
         <v>19</v>
       </c>
-      <c r="E6" s="106">
+      <c r="E6" s="101">
         <v>90</v>
       </c>
-      <c r="F6" s="106">
+      <c r="F6" s="101">
         <v>177</v>
       </c>
-      <c r="G6" s="106">
+      <c r="G6" s="101">
         <v>86</v>
       </c>
-      <c r="H6" s="106">
+      <c r="H6" s="101">
         <v>11043</v>
       </c>
-      <c r="I6" s="106">
+      <c r="I6" s="101">
         <v>16397</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="27" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="104" t="s">
+      <c r="C7" s="99" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="27">
@@ -9598,101 +9321,101 @@
         <v>67165</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="105" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="100" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="105" t="s">
+      <c r="B8" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="105" t="s">
+      <c r="C8" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="105">
+      <c r="D8" s="100">
         <v>0</v>
       </c>
-      <c r="E8" s="105">
+      <c r="E8" s="100">
         <v>0</v>
       </c>
-      <c r="F8" s="105">
+      <c r="F8" s="100">
         <v>0</v>
       </c>
-      <c r="G8" s="105">
+      <c r="G8" s="100">
         <v>0</v>
       </c>
-      <c r="H8" s="105">
+      <c r="H8" s="100">
         <v>9671560</v>
       </c>
-      <c r="I8" s="105">
+      <c r="I8" s="100">
         <v>9679631</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="105" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="105" t="s">
+      <c r="B9" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="105" t="s">
+      <c r="C9" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="105">
+      <c r="D9" s="100">
         <v>0</v>
       </c>
-      <c r="E9" s="105">
+      <c r="E9" s="100">
         <v>0</v>
       </c>
-      <c r="F9" s="105">
+      <c r="F9" s="100">
         <v>0</v>
       </c>
-      <c r="G9" s="105">
+      <c r="G9" s="100">
         <v>0</v>
       </c>
-      <c r="H9" s="105">
+      <c r="H9" s="100">
         <v>7597008</v>
       </c>
-      <c r="I9" s="105">
+      <c r="I9" s="100">
         <v>6785831</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="27" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="104" t="s">
+      <c r="C10" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="106">
+      <c r="D10" s="101">
         <v>1</v>
       </c>
-      <c r="E10" s="106">
+      <c r="E10" s="101">
         <v>20</v>
       </c>
-      <c r="F10" s="106">
+      <c r="F10" s="101">
         <v>39</v>
       </c>
-      <c r="G10" s="106">
+      <c r="G10" s="101">
         <v>160</v>
       </c>
-      <c r="H10" s="106">
+      <c r="H10" s="101">
         <v>1657</v>
       </c>
-      <c r="I10" s="106">
+      <c r="I10" s="101">
         <v>3334</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="27" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="104" t="s">
+      <c r="C11" s="99" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="27">
@@ -9714,101 +9437,101 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="105" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="100" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="105" t="s">
+      <c r="B12" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="105" t="s">
+      <c r="C12" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="105">
+      <c r="D12" s="100">
         <v>0</v>
       </c>
-      <c r="E12" s="105">
+      <c r="E12" s="100">
         <v>0</v>
       </c>
-      <c r="F12" s="105">
+      <c r="F12" s="100">
         <v>0</v>
       </c>
-      <c r="G12" s="105">
+      <c r="G12" s="100">
         <v>0</v>
       </c>
-      <c r="H12" s="105">
+      <c r="H12" s="100">
         <v>0</v>
       </c>
-      <c r="I12" s="105">
+      <c r="I12" s="100">
         <v>6485263</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="105" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="105" t="s">
+      <c r="B13" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="105" t="s">
+      <c r="C13" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="105">
+      <c r="D13" s="100">
         <v>0</v>
       </c>
-      <c r="E13" s="105">
+      <c r="E13" s="100">
         <v>0</v>
       </c>
-      <c r="F13" s="105">
+      <c r="F13" s="100">
         <v>0</v>
       </c>
-      <c r="G13" s="105">
+      <c r="G13" s="100">
         <v>0</v>
       </c>
-      <c r="H13" s="105">
+      <c r="H13" s="100">
         <v>0</v>
       </c>
-      <c r="I13" s="105">
+      <c r="I13" s="100">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="27" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="104" t="s">
+      <c r="C14" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="106">
+      <c r="D14" s="101">
         <v>1</v>
       </c>
-      <c r="E14" s="106">
+      <c r="E14" s="101">
         <v>22</v>
       </c>
-      <c r="F14" s="106">
+      <c r="F14" s="101">
         <v>24</v>
       </c>
-      <c r="G14" s="106">
+      <c r="G14" s="101">
         <v>96</v>
       </c>
-      <c r="H14" s="106">
+      <c r="H14" s="101">
         <v>1275</v>
       </c>
-      <c r="I14" s="106">
+      <c r="I14" s="101">
         <v>5177</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="27" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="104" t="s">
+      <c r="C15" s="99" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="27">
@@ -9830,83 +9553,81 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="105" t="s">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="100" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="105" t="s">
+      <c r="B16" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="105" t="s">
+      <c r="C16" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="105">
+      <c r="D16" s="100">
         <v>0</v>
       </c>
-      <c r="E16" s="105">
+      <c r="E16" s="100">
         <v>0</v>
       </c>
-      <c r="F16" s="105">
+      <c r="F16" s="100">
         <v>0</v>
       </c>
-      <c r="G16" s="105">
+      <c r="G16" s="100">
         <v>0</v>
       </c>
-      <c r="H16" s="105">
+      <c r="H16" s="100">
         <v>0</v>
       </c>
-      <c r="I16" s="107">
+      <c r="I16" s="102">
         <v>-6198802</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="105" t="s">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="105" t="s">
+      <c r="B17" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="105" t="s">
+      <c r="C17" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="105">
+      <c r="D17" s="100">
         <v>0</v>
       </c>
-      <c r="E17" s="105">
+      <c r="E17" s="100">
         <v>0</v>
       </c>
-      <c r="F17" s="105">
+      <c r="F17" s="100">
         <v>0</v>
       </c>
-      <c r="G17" s="105">
+      <c r="G17" s="100">
         <v>0</v>
       </c>
-      <c r="H17" s="105">
+      <c r="H17" s="100">
         <v>0</v>
       </c>
-      <c r="I17" s="105">
+      <c r="I17" s="100">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:C5"/>
-  <sheetFormatPr defaultColWidth="10.8285714285714" defaultRowHeight="16" outlineLevelRow="4" outlineLevelCol="2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.6642857142857" style="99" customWidth="1"/>
-    <col min="2" max="16384" width="10.8285714285714" style="1"/>
+    <col min="1" max="1" width="16.6640625" style="94" customWidth="1"/>
+    <col min="2" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="32" spans="1:3">
-      <c r="A2" s="100" t="s">
+    <row r="2" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A2" s="95" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -9916,8 +9637,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="101" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="96" t="s">
         <v>29</v>
       </c>
       <c r="B3" s="8">
@@ -9927,8 +9648,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="101" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="96" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="8">
@@ -9938,8 +9659,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="101" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="96" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="8">
@@ -9950,234 +9671,232 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AL44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="7" max="7" width="13.1642857142857" customWidth="1"/>
-    <col min="10" max="10" width="10.8285714285714" style="48"/>
+    <col min="7" max="7" width="13.1640625" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="52"/>
-    </row>
-    <row r="3" spans="11:11">
-      <c r="K3" s="52"/>
-    </row>
-    <row r="4" ht="26" spans="6:6">
-      <c r="F4" s="67" t="s">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A1" s="51"/>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="K3" s="51"/>
+    </row>
+    <row r="4" spans="1:38" ht="26" x14ac:dyDescent="0.3">
+      <c r="F4" s="66" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="52"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="76" t="s">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A5" s="51"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="75" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
-      <c r="A6" s="52"/>
-      <c r="G6" s="52" t="s">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A6" s="51"/>
+      <c r="G6" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="75"/>
-      <c r="J6" s="76" t="s">
+      <c r="I6" s="74"/>
+      <c r="J6" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="Q6" s="52" t="s">
+      <c r="Q6" s="51" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
-      <c r="A7" s="52"/>
-      <c r="G7" s="52" t="s">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A7" s="51"/>
+      <c r="G7" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="75"/>
-      <c r="J7" s="76" t="s">
+      <c r="I7" s="74"/>
+      <c r="J7" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="Q7" s="52" t="s">
+      <c r="Q7" s="51" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" ht="16.75" spans="7:22">
-      <c r="G8" s="68" t="s">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="G8" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="I8" s="77" t="s">
+      <c r="I8" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="J8" s="76" t="s">
+      <c r="J8" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="L8" s="78" t="s">
+      <c r="L8" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="M8" s="79"/>
-      <c r="N8" s="79"/>
-      <c r="Q8" s="82" t="s">
+      <c r="M8" s="78"/>
+      <c r="N8" s="78"/>
+      <c r="Q8" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="V8" s="52" t="s">
+      <c r="V8" s="51" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="9:33">
-      <c r="I9" s="75"/>
-      <c r="V9" s="88"/>
-      <c r="W9" s="89"/>
-      <c r="X9" s="89"/>
-      <c r="Y9" s="89"/>
-      <c r="Z9" s="89"/>
-      <c r="AA9" s="89"/>
-      <c r="AB9" s="89"/>
-      <c r="AC9" s="89"/>
-      <c r="AD9" s="89"/>
-      <c r="AE9" s="89"/>
-      <c r="AF9" s="89"/>
-      <c r="AG9" s="94"/>
-    </row>
-    <row r="10" customHeight="1" spans="6:33">
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="I9" s="74"/>
+      <c r="V9" s="87"/>
+      <c r="W9" s="88"/>
+      <c r="X9" s="88"/>
+      <c r="Y9" s="88"/>
+      <c r="Z9" s="88"/>
+      <c r="AA9" s="88"/>
+      <c r="AB9" s="88"/>
+      <c r="AC9" s="88"/>
+      <c r="AD9" s="88"/>
+      <c r="AE9" s="88"/>
+      <c r="AF9" s="88"/>
+      <c r="AG9" s="90"/>
+    </row>
+    <row r="10" spans="1:38" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
       <c r="I10" s="48"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="V10" s="90" t="s">
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="71"/>
+      <c r="V10" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="W10" s="91"/>
-      <c r="X10" s="91"/>
-      <c r="Y10" s="91"/>
-      <c r="Z10" s="91"/>
-      <c r="AA10" s="91"/>
-      <c r="AB10" s="91"/>
-      <c r="AC10" s="91"/>
-      <c r="AD10" s="91"/>
-      <c r="AE10" s="91"/>
-      <c r="AF10" s="91"/>
-      <c r="AG10" s="95"/>
-    </row>
-    <row r="11" customHeight="1" spans="6:33">
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
+      <c r="W10" s="114"/>
+      <c r="X10" s="114"/>
+      <c r="Y10" s="114"/>
+      <c r="Z10" s="114"/>
+      <c r="AA10" s="114"/>
+      <c r="AB10" s="114"/>
+      <c r="AC10" s="114"/>
+      <c r="AD10" s="114"/>
+      <c r="AE10" s="114"/>
+      <c r="AF10" s="114"/>
+      <c r="AG10" s="115"/>
+    </row>
+    <row r="11" spans="1:38" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
       <c r="I11" s="48"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
-      <c r="V11" s="90"/>
-      <c r="W11" s="91"/>
-      <c r="X11" s="91"/>
-      <c r="Y11" s="91"/>
-      <c r="Z11" s="91"/>
-      <c r="AA11" s="91"/>
-      <c r="AB11" s="91"/>
-      <c r="AC11" s="91"/>
-      <c r="AD11" s="91"/>
-      <c r="AE11" s="91"/>
-      <c r="AF11" s="91"/>
-      <c r="AG11" s="95"/>
-    </row>
-    <row r="12" spans="6:33">
-      <c r="F12" s="62"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="L12" s="52" t="s">
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="V11" s="113"/>
+      <c r="W11" s="114"/>
+      <c r="X11" s="114"/>
+      <c r="Y11" s="114"/>
+      <c r="Z11" s="114"/>
+      <c r="AA11" s="114"/>
+      <c r="AB11" s="114"/>
+      <c r="AC11" s="114"/>
+      <c r="AD11" s="114"/>
+      <c r="AE11" s="114"/>
+      <c r="AF11" s="114"/>
+      <c r="AG11" s="115"/>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="L12" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="P12" s="72"/>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="72"/>
-      <c r="V12" s="61"/>
-      <c r="W12" s="62"/>
-      <c r="X12" s="62"/>
-      <c r="Y12" s="62"/>
-      <c r="Z12" s="62"/>
-      <c r="AA12" s="62"/>
-      <c r="AB12" s="62"/>
-      <c r="AC12" s="62"/>
-      <c r="AD12" s="62"/>
-      <c r="AE12" s="62"/>
-      <c r="AF12" s="62"/>
+      <c r="P12" s="71"/>
+      <c r="Q12" s="71"/>
+      <c r="R12" s="71"/>
+      <c r="V12" s="60"/>
+      <c r="W12" s="61"/>
+      <c r="X12" s="61"/>
+      <c r="Y12" s="61"/>
+      <c r="Z12" s="61"/>
+      <c r="AA12" s="61"/>
+      <c r="AB12" s="61"/>
+      <c r="AC12" s="61"/>
+      <c r="AD12" s="61"/>
+      <c r="AE12" s="61"/>
+      <c r="AF12" s="61"/>
       <c r="AG12" s="39"/>
     </row>
-    <row r="13" ht="17" spans="5:33">
-      <c r="E13" s="69"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="L13" s="52" t="s">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="E13" s="68"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="L13" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="72"/>
-      <c r="Q13" s="72"/>
-      <c r="R13" s="72"/>
-      <c r="V13" s="61"/>
-      <c r="W13" s="92"/>
-      <c r="X13" s="92"/>
-      <c r="Y13" s="92"/>
-      <c r="Z13" s="92"/>
-      <c r="AA13" s="92"/>
-      <c r="AB13" s="92"/>
-      <c r="AC13" s="92"/>
-      <c r="AD13" s="92"/>
-      <c r="AE13" s="92"/>
-      <c r="AF13" s="92"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="71"/>
+      <c r="V13" s="60"/>
+      <c r="W13" s="112"/>
+      <c r="X13" s="112"/>
+      <c r="Y13" s="112"/>
+      <c r="Z13" s="112"/>
+      <c r="AA13" s="112"/>
+      <c r="AB13" s="112"/>
+      <c r="AC13" s="112"/>
+      <c r="AD13" s="112"/>
+      <c r="AE13" s="112"/>
+      <c r="AF13" s="112"/>
       <c r="AG13" s="39"/>
     </row>
-    <row r="14" spans="5:33">
-      <c r="E14" s="70"/>
-      <c r="F14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="72"/>
-      <c r="R14" s="72"/>
-      <c r="U14" s="52"/>
-      <c r="V14" s="93"/>
-      <c r="W14" s="72"/>
-      <c r="X14" s="72"/>
-      <c r="Y14" s="72"/>
-      <c r="Z14" s="72"/>
-      <c r="AA14" s="72"/>
-      <c r="AB14" s="72"/>
-      <c r="AC14" s="72"/>
-      <c r="AD14" s="72"/>
-      <c r="AE14" s="72"/>
-      <c r="AF14" s="72"/>
-      <c r="AG14" s="96"/>
-    </row>
-    <row r="15" spans="5:38">
-      <c r="E15" s="71"/>
-      <c r="F15" s="62"/>
-      <c r="H15" s="62"/>
-      <c r="P15" s="72"/>
-      <c r="Q15" s="72"/>
-      <c r="R15" s="72"/>
-      <c r="U15" s="52"/>
-      <c r="V15" s="93"/>
-      <c r="W15" s="72"/>
-      <c r="X15" s="72"/>
-      <c r="Y15" s="72"/>
-      <c r="Z15" s="72"/>
-      <c r="AA15" s="72"/>
-      <c r="AB15" s="72"/>
-      <c r="AC15" s="72"/>
-      <c r="AD15" s="72"/>
-      <c r="AE15" s="72"/>
-      <c r="AF15" s="72"/>
-      <c r="AG15" s="97" t="s">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="E14" s="69"/>
+      <c r="F14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="71"/>
+      <c r="U14" s="51"/>
+      <c r="V14" s="89"/>
+      <c r="W14" s="71"/>
+      <c r="X14" s="71"/>
+      <c r="Y14" s="71"/>
+      <c r="Z14" s="71"/>
+      <c r="AA14" s="71"/>
+      <c r="AB14" s="71"/>
+      <c r="AC14" s="71"/>
+      <c r="AD14" s="71"/>
+      <c r="AE14" s="71"/>
+      <c r="AF14" s="71"/>
+      <c r="AG14" s="91"/>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="E15" s="70"/>
+      <c r="F15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="71"/>
+      <c r="U15" s="51"/>
+      <c r="V15" s="89"/>
+      <c r="W15" s="71"/>
+      <c r="X15" s="71"/>
+      <c r="Y15" s="71"/>
+      <c r="Z15" s="71"/>
+      <c r="AA15" s="71"/>
+      <c r="AB15" s="71"/>
+      <c r="AC15" s="71"/>
+      <c r="AD15" s="71"/>
+      <c r="AE15" s="71"/>
+      <c r="AF15" s="71"/>
+      <c r="AG15" s="92" t="s">
         <v>49</v>
       </c>
       <c r="AH15" s="48"/>
@@ -10186,64 +9905,64 @@
       <c r="AK15" s="48"/>
       <c r="AL15" s="48"/>
     </row>
-    <row r="16" spans="5:38">
-      <c r="E16" s="71"/>
-      <c r="F16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="P16" s="72"/>
-      <c r="Q16" s="72"/>
-      <c r="R16" s="72"/>
-      <c r="U16" s="52"/>
-      <c r="V16" s="93"/>
-      <c r="W16" s="72"/>
-      <c r="X16" s="72"/>
-      <c r="Y16" s="72"/>
-      <c r="Z16" s="72"/>
-      <c r="AA16" s="72"/>
-      <c r="AB16" s="72"/>
-      <c r="AC16" s="72"/>
-      <c r="AD16" s="72"/>
-      <c r="AE16" s="72"/>
-      <c r="AF16" s="72"/>
-      <c r="AG16" s="97"/>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="E16" s="70"/>
+      <c r="F16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="71"/>
+      <c r="U16" s="51"/>
+      <c r="V16" s="89"/>
+      <c r="W16" s="71"/>
+      <c r="X16" s="71"/>
+      <c r="Y16" s="71"/>
+      <c r="Z16" s="71"/>
+      <c r="AA16" s="71"/>
+      <c r="AB16" s="71"/>
+      <c r="AC16" s="71"/>
+      <c r="AD16" s="71"/>
+      <c r="AE16" s="71"/>
+      <c r="AF16" s="71"/>
+      <c r="AG16" s="92"/>
       <c r="AH16" s="48"/>
-      <c r="AI16" s="98"/>
+      <c r="AI16" s="93"/>
       <c r="AJ16" s="48"/>
       <c r="AK16" s="48"/>
       <c r="AL16" s="48"/>
     </row>
-    <row r="17" spans="6:38">
-      <c r="F17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="72"/>
-      <c r="R17" s="72"/>
-      <c r="U17" s="52"/>
-      <c r="V17" s="93"/>
-      <c r="W17" s="72"/>
-      <c r="X17" s="72"/>
-      <c r="Y17" s="72"/>
-      <c r="Z17" s="72"/>
-      <c r="AA17" s="72"/>
-      <c r="AB17" s="72"/>
-      <c r="AC17" s="72"/>
-      <c r="AD17" s="72"/>
-      <c r="AE17" s="72"/>
-      <c r="AF17" s="72"/>
+    <row r="17" spans="2:38" x14ac:dyDescent="0.2">
+      <c r="F17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="71"/>
+      <c r="U17" s="51"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="71"/>
+      <c r="X17" s="71"/>
+      <c r="Y17" s="71"/>
+      <c r="Z17" s="71"/>
+      <c r="AA17" s="71"/>
+      <c r="AB17" s="71"/>
+      <c r="AC17" s="71"/>
+      <c r="AD17" s="71"/>
+      <c r="AE17" s="71"/>
+      <c r="AF17" s="71"/>
       <c r="AG17" s="39"/>
       <c r="AI17" s="48"/>
       <c r="AJ17" s="48"/>
       <c r="AK17" s="48"/>
       <c r="AL17" s="48"/>
     </row>
-    <row r="18" spans="6:38">
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="P18" s="72"/>
-      <c r="Q18" s="72"/>
-      <c r="R18" s="72"/>
-      <c r="V18" s="93"/>
+    <row r="18" spans="2:38" x14ac:dyDescent="0.2">
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="71"/>
+      <c r="V18" s="89"/>
       <c r="W18" s="48"/>
       <c r="X18" s="48"/>
       <c r="Y18" s="48"/>
@@ -10260,300 +9979,297 @@
       <c r="AK18" s="48"/>
       <c r="AL18" s="48"/>
     </row>
-    <row r="19" spans="6:33">
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="P19" s="72"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="72"/>
-      <c r="V19" s="93"/>
-      <c r="W19" s="62"/>
-      <c r="X19" s="62"/>
-      <c r="Y19" s="62"/>
-      <c r="Z19" s="62"/>
-      <c r="AA19" s="62"/>
-      <c r="AB19" s="62"/>
-      <c r="AC19" s="62"/>
-      <c r="AD19" s="62"/>
-      <c r="AE19" s="62"/>
-      <c r="AF19" s="62"/>
+    <row r="19" spans="2:38" x14ac:dyDescent="0.2">
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="71"/>
+      <c r="V19" s="89"/>
+      <c r="W19" s="61"/>
+      <c r="X19" s="61"/>
+      <c r="Y19" s="61"/>
+      <c r="Z19" s="61"/>
+      <c r="AA19" s="61"/>
+      <c r="AB19" s="61"/>
+      <c r="AC19" s="61"/>
+      <c r="AD19" s="61"/>
+      <c r="AE19" s="61"/>
+      <c r="AF19" s="61"/>
       <c r="AG19" s="39"/>
     </row>
-    <row r="20" spans="6:33">
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="P20" s="72"/>
-      <c r="Q20" s="72"/>
-      <c r="R20" s="72"/>
-      <c r="V20" s="93"/>
+    <row r="20" spans="2:38" x14ac:dyDescent="0.2">
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="71"/>
+      <c r="V20" s="89"/>
       <c r="W20" s="48"/>
-      <c r="X20" s="62"/>
-      <c r="Y20" s="62"/>
-      <c r="Z20" s="62"/>
-      <c r="AA20" s="62"/>
-      <c r="AB20" s="62"/>
-      <c r="AC20" s="62"/>
-      <c r="AD20" s="62"/>
-      <c r="AE20" s="62"/>
-      <c r="AF20" s="62"/>
+      <c r="X20" s="61"/>
+      <c r="Y20" s="61"/>
+      <c r="Z20" s="61"/>
+      <c r="AA20" s="61"/>
+      <c r="AB20" s="61"/>
+      <c r="AC20" s="61"/>
+      <c r="AD20" s="61"/>
+      <c r="AE20" s="61"/>
+      <c r="AF20" s="61"/>
       <c r="AG20" s="39"/>
     </row>
-    <row r="21" spans="6:33">
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="P21" s="72"/>
-      <c r="Q21" s="72"/>
-      <c r="R21" s="72"/>
-      <c r="V21" s="93"/>
+    <row r="21" spans="2:38" x14ac:dyDescent="0.2">
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="61"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="71"/>
+      <c r="V21" s="89"/>
       <c r="W21" s="48"/>
-      <c r="X21" s="62" t="s">
+      <c r="X21" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="Y21" s="62"/>
-      <c r="Z21" s="62"/>
-      <c r="AA21" s="62"/>
-      <c r="AB21" s="62"/>
-      <c r="AC21" s="62"/>
-      <c r="AD21" s="62"/>
-      <c r="AE21" s="62"/>
-      <c r="AF21" s="62"/>
+      <c r="Y21" s="61"/>
+      <c r="Z21" s="61"/>
+      <c r="AA21" s="61"/>
+      <c r="AB21" s="61"/>
+      <c r="AC21" s="61"/>
+      <c r="AD21" s="61"/>
+      <c r="AE21" s="61"/>
+      <c r="AF21" s="61"/>
       <c r="AG21" s="39"/>
     </row>
-    <row r="22" spans="6:33">
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="P22" s="72"/>
-      <c r="Q22" s="72"/>
-      <c r="R22" s="72"/>
-      <c r="V22" s="93"/>
+    <row r="22" spans="2:38" x14ac:dyDescent="0.2">
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="71"/>
+      <c r="V22" s="89"/>
       <c r="W22" s="48"/>
-      <c r="X22" s="62"/>
-      <c r="Y22" s="62"/>
-      <c r="Z22" s="62"/>
-      <c r="AA22" s="62"/>
-      <c r="AB22" s="62"/>
-      <c r="AC22" s="62"/>
-      <c r="AD22" s="62"/>
-      <c r="AE22" s="62"/>
-      <c r="AF22" s="62"/>
+      <c r="X22" s="61"/>
+      <c r="Y22" s="61"/>
+      <c r="Z22" s="61"/>
+      <c r="AA22" s="61"/>
+      <c r="AB22" s="61"/>
+      <c r="AC22" s="61"/>
+      <c r="AD22" s="61"/>
+      <c r="AE22" s="61"/>
+      <c r="AF22" s="61"/>
       <c r="AG22" s="39"/>
     </row>
-    <row r="23" ht="16.75" spans="6:33">
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
-      <c r="R23" s="72"/>
+    <row r="23" spans="2:38" x14ac:dyDescent="0.2">
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="71"/>
       <c r="V23" s="40"/>
-      <c r="W23" s="65"/>
-      <c r="X23" s="65"/>
-      <c r="Y23" s="65"/>
-      <c r="Z23" s="65"/>
-      <c r="AA23" s="65"/>
-      <c r="AB23" s="65"/>
-      <c r="AC23" s="65"/>
-      <c r="AD23" s="65"/>
-      <c r="AE23" s="65"/>
-      <c r="AF23" s="65"/>
-      <c r="AG23" s="66"/>
-    </row>
-    <row r="24" spans="6:18">
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="P24" s="72"/>
-      <c r="Q24" s="72"/>
-      <c r="R24" s="72"/>
-    </row>
-    <row r="31" ht="16.75"/>
-    <row r="32" spans="2:18">
-      <c r="B32" s="53"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="55"/>
-      <c r="F32" s="72"/>
-      <c r="G32" s="72"/>
-      <c r="H32" s="72"/>
-      <c r="P32" s="80"/>
-      <c r="Q32" s="83"/>
-      <c r="R32" s="84"/>
-    </row>
-    <row r="33" spans="2:18">
-      <c r="B33" s="56"/>
-      <c r="C33" s="57"/>
-      <c r="D33" s="58"/>
-      <c r="F33" s="72"/>
-      <c r="G33" s="72"/>
-      <c r="H33" s="72"/>
-      <c r="P33" s="81"/>
-      <c r="Q33" s="85"/>
-      <c r="R33" s="86"/>
-    </row>
-    <row r="34" spans="2:18">
-      <c r="B34" s="56"/>
-      <c r="C34" s="57"/>
-      <c r="D34" s="58"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="72"/>
-      <c r="P34" s="81"/>
-      <c r="Q34" s="85"/>
-      <c r="R34" s="86"/>
-    </row>
-    <row r="35" spans="2:18">
-      <c r="B35" s="56"/>
-      <c r="C35" s="59" t="s">
+      <c r="W23" s="64"/>
+      <c r="X23" s="64"/>
+      <c r="Y23" s="64"/>
+      <c r="Z23" s="64"/>
+      <c r="AA23" s="64"/>
+      <c r="AB23" s="64"/>
+      <c r="AC23" s="64"/>
+      <c r="AD23" s="64"/>
+      <c r="AE23" s="64"/>
+      <c r="AF23" s="64"/>
+      <c r="AG23" s="65"/>
+    </row>
+    <row r="24" spans="2:38" x14ac:dyDescent="0.2">
+      <c r="F24" s="61"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="71"/>
+    </row>
+    <row r="32" spans="2:38" x14ac:dyDescent="0.2">
+      <c r="B32" s="52"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="54"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="P32" s="79"/>
+      <c r="Q32" s="82"/>
+      <c r="R32" s="83"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B33" s="55"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="57"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="P33" s="80"/>
+      <c r="Q33" s="84"/>
+      <c r="R33" s="85"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B34" s="55"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="57"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="P34" s="80"/>
+      <c r="Q34" s="84"/>
+      <c r="R34" s="85"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B35" s="55"/>
+      <c r="C35" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="58"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
-      <c r="P35" s="81"/>
-      <c r="Q35" s="85"/>
-      <c r="R35" s="86"/>
-    </row>
-    <row r="36" spans="2:18">
-      <c r="B36" s="56"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="58"/>
-      <c r="F36" s="72"/>
-      <c r="G36" s="71" t="s">
+      <c r="D35" s="57"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="P35" s="80"/>
+      <c r="Q35" s="84"/>
+      <c r="R35" s="85"/>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B36" s="55"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="57"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="H36" s="72"/>
-      <c r="P36" s="81"/>
-      <c r="Q36" s="87" t="s">
+      <c r="H36" s="71"/>
+      <c r="P36" s="80"/>
+      <c r="Q36" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="R36" s="86"/>
-    </row>
-    <row r="37" spans="2:18">
-      <c r="B37" s="56"/>
-      <c r="C37" s="57"/>
-      <c r="D37" s="58"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="72"/>
-      <c r="P37" s="81"/>
-      <c r="Q37" s="85"/>
-      <c r="R37" s="86"/>
-    </row>
-    <row r="38" spans="2:18">
-      <c r="B38" s="56"/>
-      <c r="C38" s="57"/>
-      <c r="D38" s="58"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="72"/>
-      <c r="H38" s="72"/>
-      <c r="P38" s="81"/>
-      <c r="Q38" s="85"/>
-      <c r="R38" s="86"/>
-    </row>
-    <row r="39" spans="2:18">
-      <c r="B39" s="56"/>
-      <c r="C39" s="57"/>
-      <c r="D39" s="58"/>
-      <c r="F39" s="72"/>
-      <c r="G39" s="72"/>
-      <c r="H39" s="72"/>
-      <c r="P39" s="81"/>
-      <c r="Q39" s="85"/>
-      <c r="R39" s="86"/>
-    </row>
-    <row r="40" spans="2:18">
-      <c r="B40" s="56"/>
-      <c r="C40" s="60"/>
-      <c r="D40" s="58"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="72"/>
-      <c r="P40" s="81"/>
-      <c r="Q40" s="85"/>
-      <c r="R40" s="86"/>
-    </row>
-    <row r="41" spans="2:18">
-      <c r="B41" s="56"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="58"/>
-      <c r="F41" s="72"/>
-      <c r="G41" s="72"/>
-      <c r="H41" s="72"/>
-      <c r="P41" s="81"/>
-      <c r="Q41" s="85"/>
-      <c r="R41" s="86"/>
-    </row>
-    <row r="42" ht="16.75" spans="2:18">
-      <c r="B42" s="61"/>
-      <c r="C42" s="62"/>
-      <c r="D42" s="63"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="72"/>
-      <c r="H42" s="73"/>
-      <c r="P42" s="61"/>
-      <c r="Q42" s="62"/>
-      <c r="R42" s="63"/>
-    </row>
-    <row r="43" ht="16.75" spans="2:18">
-      <c r="B43" s="61"/>
-      <c r="C43" s="64" t="s">
+      <c r="R36" s="85"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B37" s="55"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="57"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="71"/>
+      <c r="P37" s="80"/>
+      <c r="Q37" s="84"/>
+      <c r="R37" s="85"/>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B38" s="55"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="57"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="P38" s="80"/>
+      <c r="Q38" s="84"/>
+      <c r="R38" s="85"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B39" s="55"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="57"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="84"/>
+      <c r="R39" s="85"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B40" s="55"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="57"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+      <c r="P40" s="80"/>
+      <c r="Q40" s="84"/>
+      <c r="R40" s="85"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B41" s="55"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="57"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
+      <c r="P41" s="80"/>
+      <c r="Q41" s="84"/>
+      <c r="R41" s="85"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B42" s="60"/>
+      <c r="C42" s="61"/>
+      <c r="D42" s="62"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="72"/>
+      <c r="P42" s="60"/>
+      <c r="Q42" s="61"/>
+      <c r="R42" s="62"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B43" s="60"/>
+      <c r="C43" s="63" t="s">
         <v>54</v>
       </c>
       <c r="D43" s="39"/>
-      <c r="F43" s="72"/>
-      <c r="G43" s="74"/>
-      <c r="H43" s="72"/>
-      <c r="P43" s="61"/>
-      <c r="Q43" s="64" t="s">
+      <c r="F43" s="71"/>
+      <c r="G43" s="73"/>
+      <c r="H43" s="71"/>
+      <c r="P43" s="60"/>
+      <c r="Q43" s="63" t="s">
         <v>54</v>
       </c>
       <c r="R43" s="39"/>
     </row>
-    <row r="44" ht="16.75" spans="2:18">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B44" s="40"/>
-      <c r="C44" s="65"/>
-      <c r="D44" s="66"/>
-      <c r="F44" s="72"/>
-      <c r="G44" s="72"/>
-      <c r="H44" s="72"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="65"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
       <c r="P44" s="40"/>
-      <c r="Q44" s="65"/>
-      <c r="R44" s="66"/>
+      <c r="Q44" s="64"/>
+      <c r="R44" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="W13:AF13"/>
     <mergeCell ref="V10:AG11"/>
   </mergeCells>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:O36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.82857142857143" customWidth="1"/>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="4" max="4" width="8.5" customWidth="1"/>
     <col min="5" max="5" width="6" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1642857142857" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" customWidth="1"/>
     <col min="7" max="7" width="28.5" customWidth="1"/>
-    <col min="8" max="8" width="22.3285714285714" customWidth="1"/>
-    <col min="9" max="9" width="13.8285714285714" style="32" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" style="32" customWidth="1"/>
     <col min="11" max="11" width="21" customWidth="1"/>
-    <col min="12" max="12" width="23.8285714285714" customWidth="1"/>
+    <col min="12" max="12" width="23.83203125" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>55</v>
       </c>
@@ -10561,20 +10277,20 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="7:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G2" s="31" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="7:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G3" s="31" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="2:2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="31"/>
     </row>
-    <row r="5" spans="7:8">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G5" s="34" t="s">
         <v>59</v>
       </c>
@@ -10582,7 +10298,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="7:8">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G6" s="36" t="s">
         <v>61</v>
       </c>
@@ -10590,7 +10306,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="7:8">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G7" s="38" t="s">
         <v>63</v>
       </c>
@@ -10598,7 +10314,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" ht="76.75" spans="7:8">
+    <row r="8" spans="1:9" ht="87" x14ac:dyDescent="0.3">
       <c r="G8" s="40" t="s">
         <v>65</v>
       </c>
@@ -10606,19 +10322,19 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="2:2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="31"/>
     </row>
-    <row r="10" spans="2:2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="31"/>
     </row>
-    <row r="11" spans="2:2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="31"/>
     </row>
-    <row r="12" spans="2:2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="31"/>
     </row>
-    <row r="13" spans="3:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C13" s="33" t="s">
         <v>67</v>
       </c>
@@ -10626,7 +10342,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="8:11">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="H18" s="42" t="s">
         <v>59</v>
       </c>
@@ -10634,7 +10350,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="8:11">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="H19" t="s">
         <v>63</v>
       </c>
@@ -10642,7 +10358,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="8:11">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="H20" s="42" t="s">
         <v>69</v>
       </c>
@@ -10650,7 +10366,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" s="32" customFormat="1" spans="2:15">
+    <row r="21" spans="2:15" s="32" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B21" s="32" t="s">
         <v>70</v>
       </c>
@@ -10658,51 +10374,51 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="6:13">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F23" s="43" t="s">
         <v>61</v>
       </c>
       <c r="G23" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H23" s="116" t="s">
         <v>73</v>
       </c>
-      <c r="K23" s="49" t="s">
+      <c r="K23" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="L23" s="50" t="s">
+      <c r="L23" s="49" t="s">
         <v>72</v>
       </c>
       <c r="M23" s="43" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="6:12">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F24" s="45"/>
       <c r="G24" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="H24" s="3"/>
-      <c r="K24" s="49"/>
+      <c r="H24" s="116"/>
+      <c r="K24" s="117"/>
       <c r="L24" s="45" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="7:12">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="G25" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H25" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="J25" s="51"/>
+      <c r="J25" s="50"/>
       <c r="K25" s="47" t="s">
         <v>75</v>
       </c>
       <c r="L25" s="45"/>
     </row>
-    <row r="26" spans="11:12">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K26" t="s">
         <v>76</v>
       </c>
@@ -10710,32 +10426,32 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="11:11">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K27" s="42" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="11:11">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K28" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="11:11">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K29" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="11:11">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K30" s="42" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="11:11">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K31" s="42" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="3:15">
+    <row r="35" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C35" s="33" t="s">
         <v>82</v>
       </c>
@@ -10746,7 +10462,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="15:15">
+    <row r="36" spans="3:15" x14ac:dyDescent="0.3">
       <c r="O36" s="33" t="s">
         <v>82</v>
       </c>
@@ -10757,35 +10473,33 @@
     <mergeCell ref="K23:K24"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G1" r:id="rId4" display="https://developer.android.google.cn/about/versions/oreo/background"/>
-    <hyperlink ref="G2" r:id="rId5" display="https://developer.android.google.cn/reference/android/support/v4/app/JobIntentService"/>
-    <hyperlink ref="G3" r:id="rId6" display="https://developer.android.google.cn/topic/libraries/architecture/workmanager/"/>
-    <hyperlink ref="A1" location="Homepage!A1" display="Home"/>
+    <hyperlink ref="G1" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="G2" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="G3" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="A1" location="Homepage!A1" display="Home" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
   </hyperlinks>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" outlineLevelCol="6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.3285714285714" customWidth="1"/>
-    <col min="6" max="6" width="24.8285714285714" customWidth="1"/>
+    <col min="1" max="1" width="26.33203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -10793,61 +10507,59 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="2:2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B3" s="31"/>
     </row>
-    <row r="4" spans="2:2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="3:3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="7:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G15" t="s">
         <v>87</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId2" display="https://developer.android.google.cn/about/versions/oreo/background"/>
-    <hyperlink ref="A1" location="Homepage!A1" display="Home"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
+    <hyperlink ref="A1" location="Homepage!A1" display="Home" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
   </hyperlinks>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:J64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.8285714285714" customWidth="1"/>
-    <col min="2" max="2" width="10.8285714285714" style="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="1"/>
     <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="5.16428571428571" customWidth="1"/>
-    <col min="5" max="5" width="10.8285714285714" style="1"/>
-    <col min="7" max="7" width="10.8285714285714" style="1"/>
+    <col min="4" max="4" width="5.1640625" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="1"/>
+    <col min="7" max="7" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" ht="17.75" spans="2:2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B2" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="8:9">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H3" s="10" t="s">
         <v>89</v>
       </c>
@@ -10855,7 +10567,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" ht="17.75" spans="2:9">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>91</v>
       </c>
@@ -10879,7 +10591,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="16.75" spans="2:6">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="6">
         <v>7</v>
       </c>
@@ -10894,10 +10606,10 @@
       </c>
       <c r="F5" s="12">
         <f t="shared" ref="F5:F20" si="0">E5/$H$4</f>
-        <v>0.212121212121212</v>
-      </c>
-    </row>
-    <row r="6" ht="17" spans="2:10">
+        <v>0.21212121212121213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6" s="6">
         <v>10</v>
       </c>
@@ -10912,7 +10624,7 @@
       </c>
       <c r="F6" s="12">
         <f t="shared" si="0"/>
-        <v>0.151515151515152</v>
+        <v>0.15151515151515152</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>93</v>
@@ -10924,7 +10636,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" s="6">
         <v>14</v>
       </c>
@@ -10939,7 +10651,7 @@
       </c>
       <c r="F7" s="12">
         <f t="shared" si="0"/>
-        <v>0.0909090909090909</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="H7" s="14" t="s">
         <v>99</v>
@@ -10949,10 +10661,10 @@
       </c>
       <c r="J7" s="28">
         <f>I7/$H$4</f>
-        <v>0.454545454545455</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
+        <v>0.45454545454545453</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="6">
         <v>5</v>
       </c>
@@ -10967,7 +10679,7 @@
       </c>
       <c r="F8" s="12">
         <f t="shared" si="0"/>
-        <v>0.0909090909090909</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="H8" s="14" t="s">
         <v>97</v>
@@ -10977,10 +10689,10 @@
       </c>
       <c r="J8" s="28">
         <f>I8/$H$4</f>
-        <v>0.424242424242424</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10">
+        <v>0.42424242424242425</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9" s="6">
         <v>16</v>
       </c>
@@ -10995,7 +10707,7 @@
       </c>
       <c r="F9" s="12">
         <f t="shared" si="0"/>
-        <v>0.0606060606060606</v>
+        <v>6.0606060606060608E-2</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>103</v>
@@ -11005,10 +10717,10 @@
       </c>
       <c r="J9" s="28">
         <f>I9/$H$4</f>
-        <v>0.0909090909090909</v>
-      </c>
-    </row>
-    <row r="10" ht="16.75" spans="2:10">
+        <v>9.0909090909090912E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B10" s="6">
         <v>12</v>
       </c>
@@ -11023,7 +10735,7 @@
       </c>
       <c r="F10" s="12">
         <f t="shared" si="0"/>
-        <v>0.0606060606060606</v>
+        <v>6.0606060606060608E-2</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>105</v>
@@ -11033,10 +10745,10 @@
       </c>
       <c r="J10" s="30">
         <f>I10/$H$4</f>
-        <v>0.0303030303030303</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6">
+        <v>3.0303030303030304E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B11" s="6">
         <v>6</v>
       </c>
@@ -11051,10 +10763,10 @@
       </c>
       <c r="F11" s="12">
         <f t="shared" si="0"/>
-        <v>0.0606060606060606</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6">
+        <v>6.0606060606060608E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B12" s="8">
         <v>15</v>
       </c>
@@ -11069,10 +10781,10 @@
       </c>
       <c r="F12" s="16">
         <f t="shared" si="0"/>
-        <v>0.0303030303030303</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6">
+        <v>3.0303030303030304E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B13" s="8">
         <v>13</v>
       </c>
@@ -11087,10 +10799,10 @@
       </c>
       <c r="F13" s="16">
         <f t="shared" si="0"/>
-        <v>0.0303030303030303</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6">
+        <v>3.0303030303030304E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" s="8">
         <v>11</v>
       </c>
@@ -11105,10 +10817,10 @@
       </c>
       <c r="F14" s="16">
         <f t="shared" si="0"/>
-        <v>0.0303030303030303</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6">
+        <v>3.0303030303030304E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" s="8">
         <v>9</v>
       </c>
@@ -11123,10 +10835,10 @@
       </c>
       <c r="F15" s="16">
         <f t="shared" si="0"/>
-        <v>0.0303030303030303</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6">
+        <v>3.0303030303030304E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16" s="8">
         <v>8</v>
       </c>
@@ -11141,10 +10853,10 @@
       </c>
       <c r="F16" s="16">
         <f t="shared" si="0"/>
-        <v>0.0303030303030303</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
+        <v>3.0303030303030304E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" s="8">
         <v>4</v>
       </c>
@@ -11159,10 +10871,10 @@
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>0.0303030303030303</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
+        <v>3.0303030303030304E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" s="8">
         <v>3</v>
       </c>
@@ -11177,10 +10889,10 @@
       </c>
       <c r="F18" s="16">
         <f t="shared" si="0"/>
-        <v>0.0303030303030303</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
+        <v>3.0303030303030304E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" s="8">
         <v>2</v>
       </c>
@@ -11195,10 +10907,10 @@
       </c>
       <c r="F19" s="16">
         <f t="shared" si="0"/>
-        <v>0.0303030303030303</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
+        <v>3.0303030303030304E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20" s="8">
         <v>1</v>
       </c>
@@ -11213,11 +10925,10 @@
       </c>
       <c r="F20" s="16">
         <f t="shared" si="0"/>
-        <v>0.0303030303030303</v>
-      </c>
-    </row>
-    <row r="59" ht="16.75"/>
-    <row r="60" spans="6:7">
+        <v>3.0303030303030304E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F60" s="17" t="s">
         <v>116</v>
       </c>
@@ -11225,7 +10936,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="61" spans="6:7">
+    <row r="61" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F61" s="19" t="s">
         <v>118</v>
       </c>
@@ -11233,7 +10944,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="6:7">
+    <row r="62" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F62" s="19" t="s">
         <v>120</v>
       </c>
@@ -11241,7 +10952,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="63" spans="6:7">
+    <row r="63" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F63" s="19" t="s">
         <v>122</v>
       </c>
@@ -11249,7 +10960,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="64" ht="16.75" spans="6:7">
+    <row r="64" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F64" s="21" t="s">
         <v>124</v>
       </c>
@@ -11258,27 +10969,24 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="H7:J10"/>
-  <sortState ref="H7:J10">
-    <sortCondition ref="J7:J10" descending="1"/>
+  <autoFilter ref="H7:J10" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H7:J10">
+    <sortCondition descending="1" ref="J7:J10"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A1" location="Homepage!A1" display="Home"/>
+    <hyperlink ref="A1" location="Homepage!A1" display="Home" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
   </hyperlinks>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>